--- a/res/hERV_DE/hERV_family_celltype.xlsx
+++ b/res/hERV_DE/hERV_family_celltype.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17185\Desktop\hERV_AD_snRNA-seq_analyze\res\hERV_DE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76BD7D86-CBE4-41CD-AC8E-3188BEF7797E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413D3DF1-F59A-47B4-A083-A0D8FEC1F94D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1140" windowWidth="12820" windowHeight="14840" xr2:uid="{4C46B9C2-8FB7-41A7-9694-9D1056BDC4CA}"/>
+    <workbookView xWindow="0" yWindow="10" windowWidth="12820" windowHeight="11400" xr2:uid="{4C46B9C2-8FB7-41A7-9694-9D1056BDC4CA}"/>
   </bookViews>
   <sheets>
     <sheet name="hERV_family_celltype" sheetId="1" r:id="rId1"/>
@@ -29,9 +29,6 @@
   </si>
   <si>
     <t>n_AD</t>
-  </si>
-  <si>
-    <t>subfamily</t>
   </si>
   <si>
     <t>p_val</t>
@@ -206,6 +203,10 @@
   </si>
   <si>
     <t>All</t>
+  </si>
+  <si>
+    <t>feature</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1180,27 +1181,27 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>26896</v>
@@ -1209,7 +1210,7 @@
         <v>31494</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1">
         <v>2.9664750781527902E-122</v>
@@ -1229,7 +1230,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>26896</v>
@@ -1238,7 +1239,7 @@
         <v>31494</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" s="1">
         <v>3.9320155344527103E-58</v>
@@ -1258,7 +1259,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>26896</v>
@@ -1267,7 +1268,7 @@
         <v>31494</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1">
         <v>3.4281114166241901E-27</v>
@@ -1287,7 +1288,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>26896</v>
@@ -1296,7 +1297,7 @@
         <v>31494</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1">
         <v>1.0165018034393599E-26</v>
@@ -1316,7 +1317,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>26896</v>
@@ -1325,7 +1326,7 @@
         <v>31494</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" s="1">
         <v>8.9533282479497797E-21</v>
@@ -1345,7 +1346,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>26896</v>
@@ -1354,7 +1355,7 @@
         <v>31494</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7" s="1">
         <v>1.5238423136484901E-20</v>
@@ -1374,7 +1375,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8">
         <v>26896</v>
@@ -1383,7 +1384,7 @@
         <v>31494</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8" s="1">
         <v>1.6604329225776799E-19</v>
@@ -1403,7 +1404,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9">
         <v>26896</v>
@@ -1412,7 +1413,7 @@
         <v>31494</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E9" s="1">
         <v>2.1164197059348201E-18</v>
@@ -1432,7 +1433,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10">
         <v>26896</v>
@@ -1441,7 +1442,7 @@
         <v>31494</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E10" s="1">
         <v>6.4407013868630496E-17</v>
@@ -1461,7 +1462,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11">
         <v>26896</v>
@@ -1470,7 +1471,7 @@
         <v>31494</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E11" s="1">
         <v>1.0238753080411499E-15</v>
@@ -1490,7 +1491,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12">
         <v>26896</v>
@@ -1499,7 +1500,7 @@
         <v>31494</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E12" s="1">
         <v>1.54415063003655E-15</v>
@@ -1519,7 +1520,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13">
         <v>26896</v>
@@ -1528,7 +1529,7 @@
         <v>31494</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E13" s="1">
         <v>1.4900867861376701E-14</v>
@@ -1548,7 +1549,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14">
         <v>26896</v>
@@ -1557,7 +1558,7 @@
         <v>31494</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E14" s="1">
         <v>1.252579677399E-12</v>
@@ -1577,7 +1578,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B15">
         <v>26896</v>
@@ -1586,7 +1587,7 @@
         <v>31494</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E15" s="1">
         <v>1.8450704470271898E-12</v>
@@ -1606,7 +1607,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B16">
         <v>26896</v>
@@ -1615,7 +1616,7 @@
         <v>31494</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E16" s="1">
         <v>3.50057705291992E-12</v>
@@ -1635,7 +1636,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B17">
         <v>26896</v>
@@ -1644,7 +1645,7 @@
         <v>31494</v>
       </c>
       <c r="D17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E17" s="1">
         <v>1.53972437255698E-9</v>
@@ -1664,7 +1665,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18">
         <v>26896</v>
@@ -1673,7 +1674,7 @@
         <v>31494</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" s="1">
         <v>4.0101483443234997E-9</v>
@@ -1693,7 +1694,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B19">
         <v>26896</v>
@@ -1702,7 +1703,7 @@
         <v>31494</v>
       </c>
       <c r="D19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E19" s="1">
         <v>9.2693418930144398E-9</v>
@@ -1722,7 +1723,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B20">
         <v>26896</v>
@@ -1731,7 +1732,7 @@
         <v>31494</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E20" s="1">
         <v>3.9485691273370498E-8</v>
@@ -1751,7 +1752,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B21">
         <v>26896</v>
@@ -1760,7 +1761,7 @@
         <v>31494</v>
       </c>
       <c r="D21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E21" s="1">
         <v>1.18959656575983E-7</v>
@@ -1780,7 +1781,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B22">
         <v>26896</v>
@@ -1789,7 +1790,7 @@
         <v>31494</v>
       </c>
       <c r="D22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E22" s="1">
         <v>1.62133688402655E-7</v>
@@ -1809,7 +1810,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B23">
         <v>26896</v>
@@ -1818,7 +1819,7 @@
         <v>31494</v>
       </c>
       <c r="D23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E23" s="1">
         <v>5.27470717312718E-7</v>
@@ -1838,7 +1839,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B24">
         <v>26896</v>
@@ -1847,7 +1848,7 @@
         <v>31494</v>
       </c>
       <c r="D24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E24" s="1">
         <v>5.7514594199932397E-7</v>
@@ -1867,7 +1868,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B25">
         <v>26896</v>
@@ -1876,7 +1877,7 @@
         <v>31494</v>
       </c>
       <c r="D25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E25" s="1">
         <v>6.5473385976250802E-7</v>
@@ -1896,7 +1897,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B26">
         <v>26896</v>
@@ -1905,7 +1906,7 @@
         <v>31494</v>
       </c>
       <c r="D26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E26" s="1">
         <v>6.6591673227370999E-7</v>
@@ -1925,7 +1926,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B27">
         <v>26896</v>
@@ -1934,7 +1935,7 @@
         <v>31494</v>
       </c>
       <c r="D27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E27" s="1">
         <v>5.2360202713017596E-6</v>
@@ -1954,7 +1955,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B28">
         <v>26896</v>
@@ -1963,7 +1964,7 @@
         <v>31494</v>
       </c>
       <c r="D28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E28" s="1">
         <v>3.5336638984204899E-5</v>
@@ -1983,7 +1984,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B29">
         <v>26896</v>
@@ -1992,7 +1993,7 @@
         <v>31494</v>
       </c>
       <c r="D29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E29">
         <v>4.4092991953626701E-4</v>
@@ -2012,7 +2013,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B30">
         <v>26896</v>
@@ -2021,7 +2022,7 @@
         <v>31494</v>
       </c>
       <c r="D30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E30">
         <v>6.8870647894698795E-4</v>
@@ -2041,7 +2042,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B31">
         <v>26896</v>
@@ -2050,7 +2051,7 @@
         <v>31494</v>
       </c>
       <c r="D31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E31">
         <v>9.2868214207785199E-4</v>
@@ -2070,7 +2071,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B32">
         <v>26896</v>
@@ -2079,7 +2080,7 @@
         <v>31494</v>
       </c>
       <c r="D32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E32">
         <v>1.4522747984137901E-3</v>
@@ -2099,7 +2100,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B33">
         <v>26896</v>
@@ -2108,7 +2109,7 @@
         <v>31494</v>
       </c>
       <c r="D33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E33">
         <v>1.7705821818606801E-3</v>
@@ -2128,7 +2129,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B34">
         <v>26896</v>
@@ -2137,7 +2138,7 @@
         <v>31494</v>
       </c>
       <c r="D34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E34">
         <v>8.6571359827432703E-3</v>
@@ -2157,7 +2158,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B35">
         <v>26896</v>
@@ -2166,7 +2167,7 @@
         <v>31494</v>
       </c>
       <c r="D35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E35">
         <v>1.4244462826066799E-2</v>
@@ -2186,7 +2187,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B36">
         <v>26896</v>
@@ -2195,7 +2196,7 @@
         <v>31494</v>
       </c>
       <c r="D36" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E36">
         <v>3.4305571103382101E-2</v>
@@ -2215,7 +2216,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B37">
         <v>26896</v>
@@ -2224,7 +2225,7 @@
         <v>31494</v>
       </c>
       <c r="D37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E37">
         <v>4.2931388608426803E-2</v>
@@ -2244,7 +2245,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B38">
         <v>26896</v>
@@ -2253,7 +2254,7 @@
         <v>31494</v>
       </c>
       <c r="D38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E38">
         <v>5.8765991979669301E-2</v>
@@ -2273,7 +2274,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B39">
         <v>26896</v>
@@ -2282,7 +2283,7 @@
         <v>31494</v>
       </c>
       <c r="D39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E39">
         <v>7.1827971928157194E-2</v>
@@ -2302,7 +2303,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B40">
         <v>26896</v>
@@ -2311,7 +2312,7 @@
         <v>31494</v>
       </c>
       <c r="D40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E40">
         <v>0.18557914757452401</v>
@@ -2331,7 +2332,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B41">
         <v>26896</v>
@@ -2340,7 +2341,7 @@
         <v>31494</v>
       </c>
       <c r="D41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E41">
         <v>0.20004221746581999</v>
@@ -2360,7 +2361,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B42">
         <v>26896</v>
@@ -2369,7 +2370,7 @@
         <v>31494</v>
       </c>
       <c r="D42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E42">
         <v>0.35373923397124701</v>
@@ -2389,7 +2390,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B43">
         <v>26896</v>
@@ -2398,7 +2399,7 @@
         <v>31494</v>
       </c>
       <c r="D43" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E43">
         <v>0.37913516651649498</v>
@@ -2418,7 +2419,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B44">
         <v>26896</v>
@@ -2427,7 +2428,7 @@
         <v>31494</v>
       </c>
       <c r="D44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E44">
         <v>0.39057209219472799</v>
@@ -2447,7 +2448,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B45">
         <v>26896</v>
@@ -2456,7 +2457,7 @@
         <v>31494</v>
       </c>
       <c r="D45" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E45">
         <v>0.76725295802833604</v>
@@ -2476,7 +2477,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B46">
         <v>26896</v>
@@ -2485,7 +2486,7 @@
         <v>31494</v>
       </c>
       <c r="D46" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E46">
         <v>0.90563484043851705</v>
@@ -2505,7 +2506,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B47">
         <v>31245</v>
@@ -2514,7 +2515,7 @@
         <v>42753</v>
       </c>
       <c r="D47" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E47" s="1">
         <v>2.9736895115673102E-32</v>
@@ -2534,7 +2535,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B48">
         <v>31245</v>
@@ -2543,7 +2544,7 @@
         <v>42753</v>
       </c>
       <c r="D48" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E48" s="1">
         <v>2.8203198122000601E-17</v>
@@ -2563,7 +2564,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B49">
         <v>31245</v>
@@ -2572,7 +2573,7 @@
         <v>42753</v>
       </c>
       <c r="D49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E49" s="1">
         <v>1.51739161491221E-16</v>
@@ -2592,7 +2593,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B50">
         <v>31245</v>
@@ -2601,7 +2602,7 @@
         <v>42753</v>
       </c>
       <c r="D50" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E50" s="1">
         <v>2.0851484444153699E-15</v>
@@ -2621,7 +2622,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B51">
         <v>31245</v>
@@ -2630,7 +2631,7 @@
         <v>42753</v>
       </c>
       <c r="D51" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E51" s="1">
         <v>4.3010184947992599E-14</v>
@@ -2650,7 +2651,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52">
         <v>31245</v>
@@ -2659,7 +2660,7 @@
         <v>42753</v>
       </c>
       <c r="D52" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E52" s="1">
         <v>1.70685822198679E-11</v>
@@ -2679,7 +2680,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B53">
         <v>31245</v>
@@ -2688,7 +2689,7 @@
         <v>42753</v>
       </c>
       <c r="D53" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E53" s="1">
         <v>1.2807545193819701E-5</v>
@@ -2708,7 +2709,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B54">
         <v>31245</v>
@@ -2717,7 +2718,7 @@
         <v>42753</v>
       </c>
       <c r="D54" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E54" s="1">
         <v>3.0710420534272799E-5</v>
@@ -2737,7 +2738,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B55">
         <v>31245</v>
@@ -2746,7 +2747,7 @@
         <v>42753</v>
       </c>
       <c r="D55" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E55" s="1">
         <v>3.2427389252227401E-5</v>
@@ -2766,7 +2767,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B56">
         <v>31245</v>
@@ -2775,7 +2776,7 @@
         <v>42753</v>
       </c>
       <c r="D56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E56" s="1">
         <v>9.2711509293162195E-5</v>
@@ -2795,7 +2796,7 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B57">
         <v>31245</v>
@@ -2804,7 +2805,7 @@
         <v>42753</v>
       </c>
       <c r="D57" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E57">
         <v>1.82569211061997E-4</v>
@@ -2824,7 +2825,7 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B58">
         <v>31245</v>
@@ -2833,7 +2834,7 @@
         <v>42753</v>
       </c>
       <c r="D58" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E58">
         <v>1.0719403693874099E-3</v>
@@ -2853,7 +2854,7 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B59">
         <v>31245</v>
@@ -2862,7 +2863,7 @@
         <v>42753</v>
       </c>
       <c r="D59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E59">
         <v>1.15724392138776E-3</v>
@@ -2882,7 +2883,7 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B60">
         <v>31245</v>
@@ -2891,7 +2892,7 @@
         <v>42753</v>
       </c>
       <c r="D60" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E60">
         <v>2.1361273087224198E-3</v>
@@ -2911,7 +2912,7 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B61">
         <v>31245</v>
@@ -2920,7 +2921,7 @@
         <v>42753</v>
       </c>
       <c r="D61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E61">
         <v>4.2332267037323004E-3</v>
@@ -2940,7 +2941,7 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B62">
         <v>31245</v>
@@ -2949,7 +2950,7 @@
         <v>42753</v>
       </c>
       <c r="D62" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E62">
         <v>5.5251826436513796E-3</v>
@@ -2969,7 +2970,7 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B63">
         <v>31245</v>
@@ -2978,7 +2979,7 @@
         <v>42753</v>
       </c>
       <c r="D63" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E63">
         <v>7.7815426965991401E-3</v>
@@ -2998,7 +2999,7 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B64">
         <v>31245</v>
@@ -3007,7 +3008,7 @@
         <v>42753</v>
       </c>
       <c r="D64" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E64">
         <v>1.31184158084408E-2</v>
@@ -3027,7 +3028,7 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B65">
         <v>31245</v>
@@ -3036,7 +3037,7 @@
         <v>42753</v>
       </c>
       <c r="D65" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E65">
         <v>1.8450521745355799E-2</v>
@@ -3056,7 +3057,7 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B66">
         <v>31245</v>
@@ -3065,7 +3066,7 @@
         <v>42753</v>
       </c>
       <c r="D66" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E66">
         <v>3.4755122775303099E-2</v>
@@ -3085,7 +3086,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B67">
         <v>31245</v>
@@ -3094,7 +3095,7 @@
         <v>42753</v>
       </c>
       <c r="D67" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E67">
         <v>3.7188697681306601E-2</v>
@@ -3114,7 +3115,7 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B68">
         <v>31245</v>
@@ -3123,7 +3124,7 @@
         <v>42753</v>
       </c>
       <c r="D68" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E68">
         <v>4.6912275441612597E-2</v>
@@ -3143,7 +3144,7 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B69">
         <v>31245</v>
@@ -3152,7 +3153,7 @@
         <v>42753</v>
       </c>
       <c r="D69" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E69">
         <v>4.7289910651254999E-2</v>
@@ -3172,7 +3173,7 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B70">
         <v>31245</v>
@@ -3181,7 +3182,7 @@
         <v>42753</v>
       </c>
       <c r="D70" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E70">
         <v>7.0857985102575793E-2</v>
@@ -3201,7 +3202,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B71">
         <v>31245</v>
@@ -3210,7 +3211,7 @@
         <v>42753</v>
       </c>
       <c r="D71" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E71">
         <v>0.12462724135843201</v>
@@ -3230,7 +3231,7 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B72">
         <v>31245</v>
@@ -3239,7 +3240,7 @@
         <v>42753</v>
       </c>
       <c r="D72" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E72">
         <v>0.14812432846335299</v>
@@ -3259,7 +3260,7 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B73">
         <v>31245</v>
@@ -3268,7 +3269,7 @@
         <v>42753</v>
       </c>
       <c r="D73" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E73">
         <v>0.20206778098497299</v>
@@ -3288,7 +3289,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B74">
         <v>31245</v>
@@ -3297,7 +3298,7 @@
         <v>42753</v>
       </c>
       <c r="D74" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E74">
         <v>0.32763304585311498</v>
@@ -3317,7 +3318,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B75">
         <v>31245</v>
@@ -3326,7 +3327,7 @@
         <v>42753</v>
       </c>
       <c r="D75" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E75">
         <v>0.35928316037548302</v>
@@ -3346,7 +3347,7 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B76">
         <v>31245</v>
@@ -3355,7 +3356,7 @@
         <v>42753</v>
       </c>
       <c r="D76" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E76">
         <v>0.37543698346895599</v>
@@ -3375,7 +3376,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B77">
         <v>31245</v>
@@ -3384,7 +3385,7 @@
         <v>42753</v>
       </c>
       <c r="D77" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E77">
         <v>0.64128935558920996</v>
@@ -3404,7 +3405,7 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B78">
         <v>31245</v>
@@ -3413,7 +3414,7 @@
         <v>42753</v>
       </c>
       <c r="D78" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E78">
         <v>0.85149800114530405</v>
@@ -3433,7 +3434,7 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B79">
         <v>31245</v>
@@ -3442,7 +3443,7 @@
         <v>42753</v>
       </c>
       <c r="D79" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E79">
         <v>0.88171858955155702</v>
@@ -3462,7 +3463,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B80">
         <v>31245</v>
@@ -3471,7 +3472,7 @@
         <v>42753</v>
       </c>
       <c r="D80" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E80">
         <v>0.91483358130685999</v>
@@ -3491,7 +3492,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B81">
         <v>31245</v>
@@ -3500,7 +3501,7 @@
         <v>42753</v>
       </c>
       <c r="D81" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E81">
         <v>0.98155315787518604</v>
@@ -3520,7 +3521,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B82">
         <v>9388</v>
@@ -3529,7 +3530,7 @@
         <v>12032</v>
       </c>
       <c r="D82" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E82" s="1">
         <v>3.5388361384984399E-17</v>
@@ -3549,7 +3550,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B83">
         <v>9388</v>
@@ -3558,7 +3559,7 @@
         <v>12032</v>
       </c>
       <c r="D83" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E83" s="1">
         <v>4.0719441650785798E-11</v>
@@ -3578,7 +3579,7 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B84">
         <v>9388</v>
@@ -3587,7 +3588,7 @@
         <v>12032</v>
       </c>
       <c r="D84" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E84" s="1">
         <v>3.2234356138319101E-8</v>
@@ -3607,7 +3608,7 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B85">
         <v>9388</v>
@@ -3616,7 +3617,7 @@
         <v>12032</v>
       </c>
       <c r="D85" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E85" s="1">
         <v>5.6413454733443502E-8</v>
@@ -3636,7 +3637,7 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B86">
         <v>9388</v>
@@ -3645,7 +3646,7 @@
         <v>12032</v>
       </c>
       <c r="D86" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E86" s="1">
         <v>1.31220973079503E-7</v>
@@ -3665,7 +3666,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B87">
         <v>9388</v>
@@ -3674,7 +3675,7 @@
         <v>12032</v>
       </c>
       <c r="D87" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E87" s="1">
         <v>1.86238914654154E-7</v>
@@ -3694,7 +3695,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B88">
         <v>9388</v>
@@ -3703,7 +3704,7 @@
         <v>12032</v>
       </c>
       <c r="D88" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E88" s="1">
         <v>6.2485849480796899E-7</v>
@@ -3723,7 +3724,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B89">
         <v>9388</v>
@@ -3732,7 +3733,7 @@
         <v>12032</v>
       </c>
       <c r="D89" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E89" s="1">
         <v>6.4716439669984101E-7</v>
@@ -3752,7 +3753,7 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B90">
         <v>9388</v>
@@ -3761,7 +3762,7 @@
         <v>12032</v>
       </c>
       <c r="D90" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E90" s="1">
         <v>2.6445416392269801E-5</v>
@@ -3781,7 +3782,7 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B91">
         <v>9388</v>
@@ -3790,7 +3791,7 @@
         <v>12032</v>
       </c>
       <c r="D91" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E91">
         <v>1.14232247676514E-4</v>
@@ -3810,7 +3811,7 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B92">
         <v>9388</v>
@@ -3819,7 +3820,7 @@
         <v>12032</v>
       </c>
       <c r="D92" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E92">
         <v>5.1503131180781101E-4</v>
@@ -3839,7 +3840,7 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B93">
         <v>9388</v>
@@ -3848,7 +3849,7 @@
         <v>12032</v>
       </c>
       <c r="D93" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E93">
         <v>1.15632495408698E-3</v>
@@ -3868,7 +3869,7 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B94">
         <v>9388</v>
@@ -3877,7 +3878,7 @@
         <v>12032</v>
       </c>
       <c r="D94" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E94">
         <v>1.4942597416208101E-3</v>
@@ -3897,7 +3898,7 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B95">
         <v>9388</v>
@@ -3906,7 +3907,7 @@
         <v>12032</v>
       </c>
       <c r="D95" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E95">
         <v>1.57042129138437E-3</v>
@@ -3926,7 +3927,7 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B96">
         <v>9388</v>
@@ -3935,7 +3936,7 @@
         <v>12032</v>
       </c>
       <c r="D96" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E96">
         <v>5.2127298932948003E-3</v>
@@ -3955,7 +3956,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B97">
         <v>9388</v>
@@ -3964,7 +3965,7 @@
         <v>12032</v>
       </c>
       <c r="D97" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E97">
         <v>5.9895192549585703E-3</v>
@@ -3984,7 +3985,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B98">
         <v>9388</v>
@@ -3993,7 +3994,7 @@
         <v>12032</v>
       </c>
       <c r="D98" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E98">
         <v>1.8591920003607199E-2</v>
@@ -4013,7 +4014,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B99">
         <v>9388</v>
@@ -4022,7 +4023,7 @@
         <v>12032</v>
       </c>
       <c r="D99" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E99">
         <v>1.9639433686066798E-2</v>
@@ -4042,7 +4043,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B100">
         <v>9388</v>
@@ -4051,7 +4052,7 @@
         <v>12032</v>
       </c>
       <c r="D100" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E100">
         <v>3.1724401493766201E-2</v>
@@ -4071,7 +4072,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B101">
         <v>9388</v>
@@ -4080,7 +4081,7 @@
         <v>12032</v>
       </c>
       <c r="D101" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E101">
         <v>4.4379216457143301E-2</v>
@@ -4100,7 +4101,7 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B102">
         <v>9388</v>
@@ -4109,7 +4110,7 @@
         <v>12032</v>
       </c>
       <c r="D102" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E102">
         <v>6.6451539489554803E-2</v>
@@ -4129,7 +4130,7 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B103">
         <v>9388</v>
@@ -4138,7 +4139,7 @@
         <v>12032</v>
       </c>
       <c r="D103" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E103">
         <v>6.8174504917566506E-2</v>
@@ -4158,7 +4159,7 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B104">
         <v>9388</v>
@@ -4167,7 +4168,7 @@
         <v>12032</v>
       </c>
       <c r="D104" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E104">
         <v>7.0362803207873206E-2</v>
@@ -4187,7 +4188,7 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B105">
         <v>9388</v>
@@ -4196,7 +4197,7 @@
         <v>12032</v>
       </c>
       <c r="D105" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E105">
         <v>0.125534275164812</v>
@@ -4216,7 +4217,7 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B106">
         <v>9388</v>
@@ -4225,7 +4226,7 @@
         <v>12032</v>
       </c>
       <c r="D106" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E106">
         <v>0.145034179202957</v>
@@ -4245,7 +4246,7 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B107">
         <v>9388</v>
@@ -4254,7 +4255,7 @@
         <v>12032</v>
       </c>
       <c r="D107" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E107">
         <v>0.32718607495183899</v>
@@ -4274,7 +4275,7 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B108">
         <v>9388</v>
@@ -4283,7 +4284,7 @@
         <v>12032</v>
       </c>
       <c r="D108" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E108">
         <v>0.42464491829314599</v>
@@ -4303,7 +4304,7 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B109">
         <v>9388</v>
@@ -4312,7 +4313,7 @@
         <v>12032</v>
       </c>
       <c r="D109" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E109">
         <v>0.42732579004135302</v>
@@ -4332,7 +4333,7 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B110">
         <v>9388</v>
@@ -4341,7 +4342,7 @@
         <v>12032</v>
       </c>
       <c r="D110" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E110">
         <v>0.46175437807577502</v>
@@ -4361,7 +4362,7 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B111">
         <v>9388</v>
@@ -4370,7 +4371,7 @@
         <v>12032</v>
       </c>
       <c r="D111" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E111">
         <v>0.47046181595275199</v>
@@ -4390,7 +4391,7 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B112">
         <v>9388</v>
@@ -4399,7 +4400,7 @@
         <v>12032</v>
       </c>
       <c r="D112" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E112">
         <v>0.54101435580211199</v>
@@ -4419,7 +4420,7 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B113">
         <v>9388</v>
@@ -4428,7 +4429,7 @@
         <v>12032</v>
       </c>
       <c r="D113" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E113">
         <v>0.68265172163314203</v>
@@ -4448,7 +4449,7 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B114">
         <v>9388</v>
@@ -4457,7 +4458,7 @@
         <v>12032</v>
       </c>
       <c r="D114" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E114">
         <v>0.79683414971937605</v>
@@ -4477,7 +4478,7 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B115">
         <v>9388</v>
@@ -4486,7 +4487,7 @@
         <v>12032</v>
       </c>
       <c r="D115" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E115">
         <v>0.95465320193871095</v>
@@ -4506,7 +4507,7 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B116">
         <v>12254</v>
@@ -4515,7 +4516,7 @@
         <v>15060</v>
       </c>
       <c r="D116" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E116" s="1">
         <v>4.5323613060245401E-74</v>
@@ -4535,7 +4536,7 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B117">
         <v>12254</v>
@@ -4544,7 +4545,7 @@
         <v>15060</v>
       </c>
       <c r="D117" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E117" s="1">
         <v>1.2228492238487199E-17</v>
@@ -4564,7 +4565,7 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B118">
         <v>12254</v>
@@ -4573,7 +4574,7 @@
         <v>15060</v>
       </c>
       <c r="D118" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E118" s="1">
         <v>2.33701085156819E-17</v>
@@ -4593,7 +4594,7 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B119">
         <v>12254</v>
@@ -4602,7 +4603,7 @@
         <v>15060</v>
       </c>
       <c r="D119" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E119" s="1">
         <v>2.4587476977141599E-15</v>
@@ -4622,7 +4623,7 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B120">
         <v>12254</v>
@@ -4631,7 +4632,7 @@
         <v>15060</v>
       </c>
       <c r="D120" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E120" s="1">
         <v>3.1159369521999698E-15</v>
@@ -4651,7 +4652,7 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B121">
         <v>12254</v>
@@ -4660,7 +4661,7 @@
         <v>15060</v>
       </c>
       <c r="D121" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E121" s="1">
         <v>1.79952693967763E-14</v>
@@ -4680,7 +4681,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B122">
         <v>12254</v>
@@ -4689,7 +4690,7 @@
         <v>15060</v>
       </c>
       <c r="D122" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E122" s="1">
         <v>2.20293234375891E-14</v>
@@ -4709,7 +4710,7 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B123">
         <v>12254</v>
@@ -4718,7 +4719,7 @@
         <v>15060</v>
       </c>
       <c r="D123" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E123" s="1">
         <v>2.29186321788798E-14</v>
@@ -4738,7 +4739,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B124">
         <v>12254</v>
@@ -4747,7 +4748,7 @@
         <v>15060</v>
       </c>
       <c r="D124" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E124" s="1">
         <v>3.5180981767024101E-14</v>
@@ -4767,7 +4768,7 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B125">
         <v>12254</v>
@@ -4776,7 +4777,7 @@
         <v>15060</v>
       </c>
       <c r="D125" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E125" s="1">
         <v>1.00152397195889E-13</v>
@@ -4796,7 +4797,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B126">
         <v>12254</v>
@@ -4805,7 +4806,7 @@
         <v>15060</v>
       </c>
       <c r="D126" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E126" s="1">
         <v>7.4083086482973398E-13</v>
@@ -4825,7 +4826,7 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B127">
         <v>12254</v>
@@ -4834,7 +4835,7 @@
         <v>15060</v>
       </c>
       <c r="D127" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E127" s="1">
         <v>9.0885388217740702E-13</v>
@@ -4854,7 +4855,7 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B128">
         <v>12254</v>
@@ -4863,7 +4864,7 @@
         <v>15060</v>
       </c>
       <c r="D128" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E128" s="1">
         <v>9.9454226347909703E-12</v>
@@ -4883,7 +4884,7 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B129">
         <v>12254</v>
@@ -4892,7 +4893,7 @@
         <v>15060</v>
       </c>
       <c r="D129" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E129" s="1">
         <v>5.5816975117507403E-11</v>
@@ -4912,7 +4913,7 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B130">
         <v>12254</v>
@@ -4921,7 +4922,7 @@
         <v>15060</v>
       </c>
       <c r="D130" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E130" s="1">
         <v>8.6718941041498696E-11</v>
@@ -4941,7 +4942,7 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B131">
         <v>12254</v>
@@ -4950,7 +4951,7 @@
         <v>15060</v>
       </c>
       <c r="D131" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E131" s="1">
         <v>3.3067622992346201E-10</v>
@@ -4970,7 +4971,7 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B132">
         <v>12254</v>
@@ -4979,7 +4980,7 @@
         <v>15060</v>
       </c>
       <c r="D132" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E132" s="1">
         <v>2.5718593768076399E-9</v>
@@ -4999,7 +5000,7 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B133">
         <v>12254</v>
@@ -5008,7 +5009,7 @@
         <v>15060</v>
       </c>
       <c r="D133" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E133" s="1">
         <v>3.3216981957894799E-9</v>
@@ -5028,7 +5029,7 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B134">
         <v>12254</v>
@@ -5037,7 +5038,7 @@
         <v>15060</v>
       </c>
       <c r="D134" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E134" s="1">
         <v>4.8718761483516598E-9</v>
@@ -5057,7 +5058,7 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B135">
         <v>12254</v>
@@ -5066,7 +5067,7 @@
         <v>15060</v>
       </c>
       <c r="D135" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E135" s="1">
         <v>2.5919995921731901E-8</v>
@@ -5086,7 +5087,7 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B136">
         <v>12254</v>
@@ -5095,7 +5096,7 @@
         <v>15060</v>
       </c>
       <c r="D136" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E136" s="1">
         <v>4.2071208729335999E-8</v>
@@ -5115,7 +5116,7 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B137">
         <v>12254</v>
@@ -5124,7 +5125,7 @@
         <v>15060</v>
       </c>
       <c r="D137" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E137" s="1">
         <v>6.7167035705469406E-8</v>
@@ -5144,7 +5145,7 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B138">
         <v>12254</v>
@@ -5153,7 +5154,7 @@
         <v>15060</v>
       </c>
       <c r="D138" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E138" s="1">
         <v>9.5685781414523697E-8</v>
@@ -5173,7 +5174,7 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B139">
         <v>12254</v>
@@ -5182,7 +5183,7 @@
         <v>15060</v>
       </c>
       <c r="D139" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E139" s="1">
         <v>1.15426218469672E-7</v>
@@ -5202,7 +5203,7 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B140">
         <v>12254</v>
@@ -5211,7 +5212,7 @@
         <v>15060</v>
       </c>
       <c r="D140" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E140" s="1">
         <v>2.9497817462371499E-7</v>
@@ -5231,7 +5232,7 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B141">
         <v>12254</v>
@@ -5240,7 +5241,7 @@
         <v>15060</v>
       </c>
       <c r="D141" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E141" s="1">
         <v>6.6401666347802601E-7</v>
@@ -5260,7 +5261,7 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B142">
         <v>12254</v>
@@ -5269,7 +5270,7 @@
         <v>15060</v>
       </c>
       <c r="D142" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E142" s="1">
         <v>6.8590648345469902E-7</v>
@@ -5289,7 +5290,7 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B143">
         <v>12254</v>
@@ -5298,7 +5299,7 @@
         <v>15060</v>
       </c>
       <c r="D143" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E143" s="1">
         <v>1.4535127737659399E-6</v>
@@ -5318,7 +5319,7 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B144">
         <v>12254</v>
@@ -5327,7 +5328,7 @@
         <v>15060</v>
       </c>
       <c r="D144" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E144" s="1">
         <v>6.6663928257133999E-6</v>
@@ -5347,7 +5348,7 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B145">
         <v>12254</v>
@@ -5356,7 +5357,7 @@
         <v>15060</v>
       </c>
       <c r="D145" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E145" s="1">
         <v>1.01206372103782E-5</v>
@@ -5376,7 +5377,7 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B146">
         <v>12254</v>
@@ -5385,7 +5386,7 @@
         <v>15060</v>
       </c>
       <c r="D146" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E146" s="1">
         <v>1.1553958257967299E-5</v>
@@ -5405,7 +5406,7 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B147">
         <v>12254</v>
@@ -5414,7 +5415,7 @@
         <v>15060</v>
       </c>
       <c r="D147" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E147" s="1">
         <v>6.4687756827178496E-5</v>
@@ -5434,7 +5435,7 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B148">
         <v>12254</v>
@@ -5443,7 +5444,7 @@
         <v>15060</v>
       </c>
       <c r="D148" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E148" s="1">
         <v>7.3521206139425194E-5</v>
@@ -5463,7 +5464,7 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B149">
         <v>12254</v>
@@ -5472,7 +5473,7 @@
         <v>15060</v>
       </c>
       <c r="D149" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E149">
         <v>1.6193946259178299E-4</v>
@@ -5492,7 +5493,7 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B150">
         <v>12254</v>
@@ -5501,7 +5502,7 @@
         <v>15060</v>
       </c>
       <c r="D150" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E150">
         <v>2.3191699629753301E-4</v>
@@ -5521,7 +5522,7 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B151">
         <v>12254</v>
@@ -5530,7 +5531,7 @@
         <v>15060</v>
       </c>
       <c r="D151" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E151">
         <v>2.4053892656701199E-4</v>
@@ -5550,7 +5551,7 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B152">
         <v>12254</v>
@@ -5559,7 +5560,7 @@
         <v>15060</v>
       </c>
       <c r="D152" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E152">
         <v>5.94522938226033E-4</v>
@@ -5579,7 +5580,7 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B153">
         <v>12254</v>
@@ -5588,7 +5589,7 @@
         <v>15060</v>
       </c>
       <c r="D153" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E153">
         <v>1.3246649483523601E-3</v>
@@ -5608,7 +5609,7 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B154">
         <v>12254</v>
@@ -5617,7 +5618,7 @@
         <v>15060</v>
       </c>
       <c r="D154" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E154">
         <v>1.6571477462979901E-3</v>
@@ -5637,7 +5638,7 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B155">
         <v>12254</v>
@@ -5646,7 +5647,7 @@
         <v>15060</v>
       </c>
       <c r="D155" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E155">
         <v>5.73397768707367E-3</v>
@@ -5666,7 +5667,7 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B156">
         <v>12254</v>
@@ -5675,7 +5676,7 @@
         <v>15060</v>
       </c>
       <c r="D156" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E156">
         <v>3.76872917988764E-2</v>
@@ -5695,7 +5696,7 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B157">
         <v>12254</v>
@@ -5704,7 +5705,7 @@
         <v>15060</v>
       </c>
       <c r="D157" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E157">
         <v>0.53868127619162198</v>
@@ -5724,7 +5725,7 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B158">
         <v>12254</v>
@@ -5733,7 +5734,7 @@
         <v>15060</v>
       </c>
       <c r="D158" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E158">
         <v>0.63795811547728098</v>
@@ -5753,7 +5754,7 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B159">
         <v>732</v>
@@ -5762,7 +5763,7 @@
         <v>1884</v>
       </c>
       <c r="D159" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E159">
         <v>0.13027023346977901</v>
@@ -5782,7 +5783,7 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B160">
         <v>732</v>
@@ -5791,7 +5792,7 @@
         <v>1884</v>
       </c>
       <c r="D160" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E160">
         <v>0.15554164247031799</v>
@@ -5811,7 +5812,7 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B161">
         <v>732</v>
@@ -5820,7 +5821,7 @@
         <v>1884</v>
       </c>
       <c r="D161" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E161">
         <v>0.20663529360375199</v>
@@ -5840,7 +5841,7 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B162">
         <v>732</v>
@@ -5849,7 +5850,7 @@
         <v>1884</v>
       </c>
       <c r="D162" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E162">
         <v>0.21726167961123799</v>
@@ -5869,7 +5870,7 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B163">
         <v>732</v>
@@ -5878,7 +5879,7 @@
         <v>1884</v>
       </c>
       <c r="D163" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E163">
         <v>0.225379088745807</v>
@@ -5898,7 +5899,7 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B164">
         <v>732</v>
@@ -5907,7 +5908,7 @@
         <v>1884</v>
       </c>
       <c r="D164" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E164">
         <v>0.246112279990049</v>
@@ -5927,7 +5928,7 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B165">
         <v>732</v>
@@ -5936,7 +5937,7 @@
         <v>1884</v>
       </c>
       <c r="D165" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E165">
         <v>0.25154044251177399</v>
@@ -5956,7 +5957,7 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B166">
         <v>732</v>
@@ -5965,7 +5966,7 @@
         <v>1884</v>
       </c>
       <c r="D166" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E166">
         <v>0.30874773003838302</v>
@@ -5985,7 +5986,7 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B167">
         <v>732</v>
@@ -5994,7 +5995,7 @@
         <v>1884</v>
       </c>
       <c r="D167" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E167">
         <v>0.32226397568209297</v>
@@ -6014,7 +6015,7 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B168">
         <v>732</v>
@@ -6023,7 +6024,7 @@
         <v>1884</v>
       </c>
       <c r="D168" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E168">
         <v>0.32772606947177502</v>
@@ -6043,7 +6044,7 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B169">
         <v>732</v>
@@ -6052,7 +6053,7 @@
         <v>1884</v>
       </c>
       <c r="D169" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E169">
         <v>0.331441616439347</v>
@@ -6072,7 +6073,7 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B170">
         <v>732</v>
@@ -6081,7 +6082,7 @@
         <v>1884</v>
       </c>
       <c r="D170" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E170">
         <v>0.34940638721979</v>
@@ -6101,7 +6102,7 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B171">
         <v>732</v>
@@ -6110,7 +6111,7 @@
         <v>1884</v>
       </c>
       <c r="D171" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E171">
         <v>0.38258968329209803</v>
@@ -6130,7 +6131,7 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B172">
         <v>732</v>
@@ -6139,7 +6140,7 @@
         <v>1884</v>
       </c>
       <c r="D172" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E172">
         <v>0.40868188718418902</v>
@@ -6159,7 +6160,7 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B173">
         <v>732</v>
@@ -6168,7 +6169,7 @@
         <v>1884</v>
       </c>
       <c r="D173" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E173">
         <v>0.45801943602379602</v>
@@ -6188,7 +6189,7 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B174">
         <v>732</v>
@@ -6197,7 +6198,7 @@
         <v>1884</v>
       </c>
       <c r="D174" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E174">
         <v>0.51328646310187598</v>
@@ -6217,7 +6218,7 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B175">
         <v>732</v>
@@ -6226,7 +6227,7 @@
         <v>1884</v>
       </c>
       <c r="D175" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E175">
         <v>0.52735763261704505</v>
@@ -6246,7 +6247,7 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B176">
         <v>732</v>
@@ -6255,7 +6256,7 @@
         <v>1884</v>
       </c>
       <c r="D176" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E176">
         <v>0.56075536092587297</v>
@@ -6275,7 +6276,7 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B177">
         <v>732</v>
@@ -6284,7 +6285,7 @@
         <v>1884</v>
       </c>
       <c r="D177" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E177">
         <v>0.57153654487071504</v>
@@ -6304,7 +6305,7 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B178">
         <v>732</v>
@@ -6313,7 +6314,7 @@
         <v>1884</v>
       </c>
       <c r="D178" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E178">
         <v>0.69188132746563802</v>
@@ -6333,7 +6334,7 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B179">
         <v>732</v>
@@ -6342,7 +6343,7 @@
         <v>1884</v>
       </c>
       <c r="D179" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E179">
         <v>0.73628389476325096</v>
@@ -6362,7 +6363,7 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B180">
         <v>732</v>
@@ -6371,7 +6372,7 @@
         <v>1884</v>
       </c>
       <c r="D180" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E180">
         <v>0.802094451504204</v>
@@ -6391,7 +6392,7 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B181">
         <v>732</v>
@@ -6400,7 +6401,7 @@
         <v>1884</v>
       </c>
       <c r="D181" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E181">
         <v>0.80567388084202796</v>
@@ -6420,7 +6421,7 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B182">
         <v>732</v>
@@ -6429,7 +6430,7 @@
         <v>1884</v>
       </c>
       <c r="D182" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E182">
         <v>0.84480251790255401</v>
@@ -6449,7 +6450,7 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B183">
         <v>732</v>
@@ -6458,7 +6459,7 @@
         <v>1884</v>
       </c>
       <c r="D183" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E183">
         <v>0.90765004986557896</v>
@@ -6478,7 +6479,7 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B184">
         <v>732</v>
@@ -6487,7 +6488,7 @@
         <v>1884</v>
       </c>
       <c r="D184" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E184">
         <v>0.98196550234668101</v>
@@ -6507,7 +6508,7 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B185">
         <v>4346</v>
@@ -6516,7 +6517,7 @@
         <v>6060</v>
       </c>
       <c r="D185" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E185" s="1">
         <v>4.2413418855945399E-14</v>
@@ -6536,7 +6537,7 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B186">
         <v>4346</v>
@@ -6545,7 +6546,7 @@
         <v>6060</v>
       </c>
       <c r="D186" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E186" s="1">
         <v>8.51986240773462E-12</v>
@@ -6565,7 +6566,7 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B187">
         <v>4346</v>
@@ -6574,7 +6575,7 @@
         <v>6060</v>
       </c>
       <c r="D187" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E187" s="1">
         <v>8.4310667418983997E-11</v>
@@ -6594,7 +6595,7 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B188">
         <v>4346</v>
@@ -6603,7 +6604,7 @@
         <v>6060</v>
       </c>
       <c r="D188" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E188" s="1">
         <v>8.7416829671259499E-8</v>
@@ -6623,7 +6624,7 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B189">
         <v>4346</v>
@@ -6632,7 +6633,7 @@
         <v>6060</v>
       </c>
       <c r="D189" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E189" s="1">
         <v>1.8089823757051401E-7</v>
@@ -6652,7 +6653,7 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B190">
         <v>4346</v>
@@ -6661,7 +6662,7 @@
         <v>6060</v>
       </c>
       <c r="D190" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E190" s="1">
         <v>1.9638941667654599E-7</v>
@@ -6681,7 +6682,7 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B191">
         <v>4346</v>
@@ -6690,7 +6691,7 @@
         <v>6060</v>
       </c>
       <c r="D191" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E191" s="1">
         <v>2.9269339336039598E-7</v>
@@ -6710,7 +6711,7 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B192">
         <v>4346</v>
@@ -6719,7 +6720,7 @@
         <v>6060</v>
       </c>
       <c r="D192" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E192" s="1">
         <v>7.9863013900713596E-7</v>
@@ -6739,7 +6740,7 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B193">
         <v>4346</v>
@@ -6748,7 +6749,7 @@
         <v>6060</v>
       </c>
       <c r="D193" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E193" s="1">
         <v>1.8396043197090799E-6</v>
@@ -6768,7 +6769,7 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B194">
         <v>4346</v>
@@ -6777,7 +6778,7 @@
         <v>6060</v>
       </c>
       <c r="D194" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E194" s="1">
         <v>2.0246413230112398E-6</v>
@@ -6797,7 +6798,7 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B195">
         <v>4346</v>
@@ -6806,7 +6807,7 @@
         <v>6060</v>
       </c>
       <c r="D195" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E195" s="1">
         <v>3.3794101441706502E-6</v>
@@ -6826,7 +6827,7 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B196">
         <v>4346</v>
@@ -6835,7 +6836,7 @@
         <v>6060</v>
       </c>
       <c r="D196" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E196" s="1">
         <v>2.05555518645668E-5</v>
@@ -6855,7 +6856,7 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B197">
         <v>4346</v>
@@ -6864,7 +6865,7 @@
         <v>6060</v>
       </c>
       <c r="D197" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E197" s="1">
         <v>2.5328672157644599E-5</v>
@@ -6884,7 +6885,7 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B198">
         <v>4346</v>
@@ -6893,7 +6894,7 @@
         <v>6060</v>
       </c>
       <c r="D198" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E198" s="1">
         <v>4.5308126893393803E-5</v>
@@ -6913,7 +6914,7 @@
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B199">
         <v>4346</v>
@@ -6922,7 +6923,7 @@
         <v>6060</v>
       </c>
       <c r="D199" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E199" s="1">
         <v>9.2870169744840603E-5</v>
@@ -6942,7 +6943,7 @@
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B200">
         <v>4346</v>
@@ -6951,7 +6952,7 @@
         <v>6060</v>
       </c>
       <c r="D200" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E200" s="1">
         <v>9.9087869408258597E-5</v>
@@ -6971,7 +6972,7 @@
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B201">
         <v>4346</v>
@@ -6980,7 +6981,7 @@
         <v>6060</v>
       </c>
       <c r="D201" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E201">
         <v>1.04151195029998E-4</v>
@@ -7000,7 +7001,7 @@
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B202">
         <v>4346</v>
@@ -7009,7 +7010,7 @@
         <v>6060</v>
       </c>
       <c r="D202" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E202">
         <v>7.6287398868027899E-4</v>
@@ -7029,7 +7030,7 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B203">
         <v>4346</v>
@@ -7038,7 +7039,7 @@
         <v>6060</v>
       </c>
       <c r="D203" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E203">
         <v>7.7331799283106696E-4</v>
@@ -7058,7 +7059,7 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B204">
         <v>4346</v>
@@ -7067,7 +7068,7 @@
         <v>6060</v>
       </c>
       <c r="D204" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E204">
         <v>7.7653914475341501E-4</v>
@@ -7087,7 +7088,7 @@
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B205">
         <v>4346</v>
@@ -7096,7 +7097,7 @@
         <v>6060</v>
       </c>
       <c r="D205" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E205">
         <v>1.7547749528147999E-3</v>
@@ -7116,7 +7117,7 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B206">
         <v>4346</v>
@@ -7125,7 +7126,7 @@
         <v>6060</v>
       </c>
       <c r="D206" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E206">
         <v>2.35217433375554E-3</v>
@@ -7145,7 +7146,7 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B207">
         <v>4346</v>
@@ -7154,7 +7155,7 @@
         <v>6060</v>
       </c>
       <c r="D207" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E207">
         <v>5.9205009141207196E-3</v>
@@ -7174,7 +7175,7 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B208">
         <v>4346</v>
@@ -7183,7 +7184,7 @@
         <v>6060</v>
       </c>
       <c r="D208" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E208">
         <v>6.93763751533958E-3</v>
@@ -7203,7 +7204,7 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B209">
         <v>4346</v>
@@ -7212,7 +7213,7 @@
         <v>6060</v>
       </c>
       <c r="D209" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E209">
         <v>1.22953818522173E-2</v>
@@ -7232,7 +7233,7 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B210">
         <v>4346</v>
@@ -7241,7 +7242,7 @@
         <v>6060</v>
       </c>
       <c r="D210" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E210">
         <v>1.28749880351028E-2</v>
@@ -7261,7 +7262,7 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B211">
         <v>4346</v>
@@ -7270,7 +7271,7 @@
         <v>6060</v>
       </c>
       <c r="D211" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E211">
         <v>6.5408611121533303E-2</v>
@@ -7290,7 +7291,7 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B212">
         <v>4346</v>
@@ -7299,7 +7300,7 @@
         <v>6060</v>
       </c>
       <c r="D212" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E212">
         <v>8.0621289036513402E-2</v>
@@ -7319,7 +7320,7 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B213">
         <v>4346</v>
@@ -7328,7 +7329,7 @@
         <v>6060</v>
       </c>
       <c r="D213" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E213">
         <v>0.40730757943791801</v>
@@ -7348,7 +7349,7 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B214">
         <v>5911</v>
@@ -7357,7 +7358,7 @@
         <v>6954</v>
       </c>
       <c r="D214" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E214" s="1">
         <v>7.2564056859891702E-9</v>
@@ -7377,7 +7378,7 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B215">
         <v>5911</v>
@@ -7386,7 +7387,7 @@
         <v>6954</v>
       </c>
       <c r="D215" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E215" s="1">
         <v>3.6842595598277502E-5</v>
@@ -7406,7 +7407,7 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B216">
         <v>5911</v>
@@ -7415,7 +7416,7 @@
         <v>6954</v>
       </c>
       <c r="D216" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E216" s="1">
         <v>5.96920647057365E-5</v>
@@ -7435,7 +7436,7 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B217">
         <v>5911</v>
@@ -7444,7 +7445,7 @@
         <v>6954</v>
       </c>
       <c r="D217" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E217">
         <v>1.2924951936765501E-4</v>
@@ -7464,7 +7465,7 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B218">
         <v>5911</v>
@@ -7473,7 +7474,7 @@
         <v>6954</v>
       </c>
       <c r="D218" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E218">
         <v>4.9139705988229003E-3</v>
@@ -7493,7 +7494,7 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B219">
         <v>5911</v>
@@ -7502,7 +7503,7 @@
         <v>6954</v>
       </c>
       <c r="D219" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E219">
         <v>5.0831355526244496E-3</v>
@@ -7522,7 +7523,7 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B220">
         <v>5911</v>
@@ -7531,7 +7532,7 @@
         <v>6954</v>
       </c>
       <c r="D220" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E220">
         <v>1.36060463425442E-2</v>
@@ -7551,7 +7552,7 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B221">
         <v>5911</v>
@@ -7560,7 +7561,7 @@
         <v>6954</v>
       </c>
       <c r="D221" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E221">
         <v>1.53521696326476E-2</v>
@@ -7580,7 +7581,7 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B222">
         <v>5911</v>
@@ -7589,7 +7590,7 @@
         <v>6954</v>
       </c>
       <c r="D222" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E222">
         <v>2.0598034748605599E-2</v>
@@ -7609,7 +7610,7 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B223">
         <v>5911</v>
@@ -7618,7 +7619,7 @@
         <v>6954</v>
       </c>
       <c r="D223" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E223">
         <v>2.54663487773783E-2</v>
@@ -7638,7 +7639,7 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B224">
         <v>5911</v>
@@ -7647,7 +7648,7 @@
         <v>6954</v>
       </c>
       <c r="D224" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E224">
         <v>3.63904725770159E-2</v>
@@ -7667,7 +7668,7 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B225">
         <v>5911</v>
@@ -7676,7 +7677,7 @@
         <v>6954</v>
       </c>
       <c r="D225" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E225">
         <v>5.0468537872276301E-2</v>
@@ -7696,7 +7697,7 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B226">
         <v>5911</v>
@@ -7705,7 +7706,7 @@
         <v>6954</v>
       </c>
       <c r="D226" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E226">
         <v>5.8700621649548403E-2</v>
@@ -7725,7 +7726,7 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B227">
         <v>5911</v>
@@ -7734,7 +7735,7 @@
         <v>6954</v>
       </c>
       <c r="D227" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E227">
         <v>7.0448635022036493E-2</v>
@@ -7754,7 +7755,7 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B228">
         <v>5911</v>
@@ -7763,7 +7764,7 @@
         <v>6954</v>
       </c>
       <c r="D228" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E228">
         <v>8.5697916294694004E-2</v>
@@ -7783,7 +7784,7 @@
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B229">
         <v>5911</v>
@@ -7792,7 +7793,7 @@
         <v>6954</v>
       </c>
       <c r="D229" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E229">
         <v>0.106777088897397</v>
@@ -7812,7 +7813,7 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B230">
         <v>5911</v>
@@ -7821,7 +7822,7 @@
         <v>6954</v>
       </c>
       <c r="D230" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E230">
         <v>0.107238372862705</v>
@@ -7841,7 +7842,7 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B231">
         <v>5911</v>
@@ -7850,7 +7851,7 @@
         <v>6954</v>
       </c>
       <c r="D231" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E231">
         <v>0.11302808262694899</v>
@@ -7870,7 +7871,7 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B232">
         <v>5911</v>
@@ -7879,7 +7880,7 @@
         <v>6954</v>
       </c>
       <c r="D232" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E232">
         <v>0.113825611806134</v>
@@ -7899,7 +7900,7 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B233">
         <v>5911</v>
@@ -7908,7 +7909,7 @@
         <v>6954</v>
       </c>
       <c r="D233" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E233">
         <v>0.1298336951082</v>
@@ -7928,7 +7929,7 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B234">
         <v>5911</v>
@@ -7937,7 +7938,7 @@
         <v>6954</v>
       </c>
       <c r="D234" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E234">
         <v>0.13901530417064101</v>
@@ -7957,7 +7958,7 @@
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B235">
         <v>5911</v>
@@ -7966,7 +7967,7 @@
         <v>6954</v>
       </c>
       <c r="D235" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E235">
         <v>0.15989022327957</v>
@@ -7986,7 +7987,7 @@
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B236">
         <v>5911</v>
@@ -7995,7 +7996,7 @@
         <v>6954</v>
       </c>
       <c r="D236" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E236">
         <v>0.16032911205710901</v>
@@ -8015,7 +8016,7 @@
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B237">
         <v>5911</v>
@@ -8024,7 +8025,7 @@
         <v>6954</v>
       </c>
       <c r="D237" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E237">
         <v>0.16122588181445399</v>
@@ -8044,7 +8045,7 @@
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B238">
         <v>5911</v>
@@ -8053,7 +8054,7 @@
         <v>6954</v>
       </c>
       <c r="D238" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E238">
         <v>0.17308814511359799</v>
@@ -8073,7 +8074,7 @@
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B239">
         <v>5911</v>
@@ -8082,7 +8083,7 @@
         <v>6954</v>
       </c>
       <c r="D239" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E239">
         <v>0.26889894339731102</v>
@@ -8102,7 +8103,7 @@
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B240">
         <v>5911</v>
@@ -8111,7 +8112,7 @@
         <v>6954</v>
       </c>
       <c r="D240" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E240">
         <v>0.27557991763175199</v>
@@ -8131,7 +8132,7 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B241">
         <v>5911</v>
@@ -8140,7 +8141,7 @@
         <v>6954</v>
       </c>
       <c r="D241" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E241">
         <v>0.31964244946186099</v>
@@ -8160,7 +8161,7 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B242">
         <v>5911</v>
@@ -8169,7 +8170,7 @@
         <v>6954</v>
       </c>
       <c r="D242" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E242">
         <v>0.38596673881942001</v>
@@ -8189,7 +8190,7 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B243">
         <v>5911</v>
@@ -8198,7 +8199,7 @@
         <v>6954</v>
       </c>
       <c r="D243" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E243">
         <v>0.44708534038476999</v>
@@ -8218,7 +8219,7 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B244">
         <v>5911</v>
@@ -8227,7 +8228,7 @@
         <v>6954</v>
       </c>
       <c r="D244" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E244">
         <v>0.46414808307826499</v>
@@ -8247,7 +8248,7 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B245">
         <v>5911</v>
@@ -8256,7 +8257,7 @@
         <v>6954</v>
       </c>
       <c r="D245" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E245">
         <v>0.60527391729332503</v>
@@ -8276,7 +8277,7 @@
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B246">
         <v>5911</v>
@@ -8285,7 +8286,7 @@
         <v>6954</v>
       </c>
       <c r="D246" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E246">
         <v>0.657156023497381</v>
@@ -8305,7 +8306,7 @@
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B247">
         <v>5911</v>
@@ -8314,7 +8315,7 @@
         <v>6954</v>
       </c>
       <c r="D247" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E247">
         <v>0.69728874266822904</v>
@@ -8334,7 +8335,7 @@
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B248">
         <v>5911</v>
@@ -8343,7 +8344,7 @@
         <v>6954</v>
       </c>
       <c r="D248" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E248">
         <v>0.72396201366120505</v>
@@ -8363,7 +8364,7 @@
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B249">
         <v>5911</v>
@@ -8372,7 +8373,7 @@
         <v>6954</v>
       </c>
       <c r="D249" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E249">
         <v>0.76951381056569801</v>
@@ -8392,7 +8393,7 @@
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B250">
         <v>5911</v>
@@ -8401,7 +8402,7 @@
         <v>6954</v>
       </c>
       <c r="D250" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E250">
         <v>0.77792279236088002</v>
@@ -8421,7 +8422,7 @@
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B251">
         <v>5911</v>
@@ -8430,7 +8431,7 @@
         <v>6954</v>
       </c>
       <c r="D251" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E251">
         <v>0.95040181316985695</v>
@@ -8450,7 +8451,7 @@
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B252">
         <v>90772</v>
@@ -8459,7 +8460,7 @@
         <v>116237</v>
       </c>
       <c r="D252" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E252" s="1">
         <v>7.01371269168221E-130</v>
@@ -8479,7 +8480,7 @@
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B253">
         <v>90772</v>
@@ -8488,7 +8489,7 @@
         <v>116237</v>
       </c>
       <c r="D253" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E253" s="1">
         <v>1.4046872393835E-59</v>
@@ -8508,7 +8509,7 @@
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B254">
         <v>90772</v>
@@ -8517,7 +8518,7 @@
         <v>116237</v>
       </c>
       <c r="D254" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E254" s="1">
         <v>1.2274011462882399E-39</v>
@@ -8537,7 +8538,7 @@
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B255">
         <v>90772</v>
@@ -8546,7 +8547,7 @@
         <v>116237</v>
       </c>
       <c r="D255" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E255" s="1">
         <v>1.08785848349624E-32</v>
@@ -8566,7 +8567,7 @@
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B256">
         <v>90772</v>
@@ -8575,7 +8576,7 @@
         <v>116237</v>
       </c>
       <c r="D256" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E256" s="1">
         <v>5.1730411581432E-31</v>
@@ -8595,7 +8596,7 @@
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B257">
         <v>90772</v>
@@ -8604,7 +8605,7 @@
         <v>116237</v>
       </c>
       <c r="D257" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E257" s="1">
         <v>2.4541154884799901E-24</v>
@@ -8624,7 +8625,7 @@
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B258">
         <v>90772</v>
@@ -8633,7 +8634,7 @@
         <v>116237</v>
       </c>
       <c r="D258" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E258" s="1">
         <v>1.28437118596672E-19</v>
@@ -8653,7 +8654,7 @@
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B259">
         <v>90772</v>
@@ -8662,7 +8663,7 @@
         <v>116237</v>
       </c>
       <c r="D259" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E259" s="1">
         <v>9.7616829030088908E-19</v>
@@ -8682,7 +8683,7 @@
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B260">
         <v>90772</v>
@@ -8691,7 +8692,7 @@
         <v>116237</v>
       </c>
       <c r="D260" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E260" s="1">
         <v>3.17314936252443E-17</v>
@@ -8711,7 +8712,7 @@
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B261">
         <v>90772</v>
@@ -8720,7 +8721,7 @@
         <v>116237</v>
       </c>
       <c r="D261" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E261" s="1">
         <v>5.0077976923406101E-17</v>
@@ -8740,7 +8741,7 @@
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B262">
         <v>90772</v>
@@ -8749,7 +8750,7 @@
         <v>116237</v>
       </c>
       <c r="D262" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E262" s="1">
         <v>1.2496875178065699E-15</v>
@@ -8769,7 +8770,7 @@
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B263">
         <v>90772</v>
@@ -8778,7 +8779,7 @@
         <v>116237</v>
       </c>
       <c r="D263" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E263" s="1">
         <v>3.8772566581190498E-13</v>
@@ -8798,7 +8799,7 @@
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B264">
         <v>90772</v>
@@ -8807,7 +8808,7 @@
         <v>116237</v>
       </c>
       <c r="D264" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E264" s="1">
         <v>6.7587526551266699E-12</v>
@@ -8827,7 +8828,7 @@
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B265">
         <v>90772</v>
@@ -8836,7 +8837,7 @@
         <v>116237</v>
       </c>
       <c r="D265" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E265" s="1">
         <v>2.7650964292408999E-11</v>
@@ -8856,7 +8857,7 @@
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B266">
         <v>90772</v>
@@ -8865,7 +8866,7 @@
         <v>116237</v>
       </c>
       <c r="D266" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E266" s="1">
         <v>7.2250730155896402E-10</v>
@@ -8885,7 +8886,7 @@
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B267">
         <v>90772</v>
@@ -8894,7 +8895,7 @@
         <v>116237</v>
       </c>
       <c r="D267" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E267" s="1">
         <v>7.2486684502447204E-10</v>
@@ -8914,7 +8915,7 @@
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B268">
         <v>90772</v>
@@ -8923,7 +8924,7 @@
         <v>116237</v>
       </c>
       <c r="D268" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E268" s="1">
         <v>2.6765651020947701E-9</v>
@@ -8943,7 +8944,7 @@
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B269">
         <v>90772</v>
@@ -8952,7 +8953,7 @@
         <v>116237</v>
       </c>
       <c r="D269" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E269" s="1">
         <v>7.7997418022656203E-9</v>
@@ -8972,7 +8973,7 @@
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B270">
         <v>90772</v>
@@ -8981,7 +8982,7 @@
         <v>116237</v>
       </c>
       <c r="D270" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E270" s="1">
         <v>1.8998109946919401E-8</v>
@@ -9001,7 +9002,7 @@
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B271">
         <v>90772</v>
@@ -9010,7 +9011,7 @@
         <v>116237</v>
       </c>
       <c r="D271" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E271" s="1">
         <v>1.34321150449374E-7</v>
@@ -9030,7 +9031,7 @@
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B272">
         <v>90772</v>
@@ -9039,7 +9040,7 @@
         <v>116237</v>
       </c>
       <c r="D272" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E272" s="1">
         <v>1.31886144878075E-6</v>
@@ -9059,7 +9060,7 @@
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B273">
         <v>90772</v>
@@ -9068,7 +9069,7 @@
         <v>116237</v>
       </c>
       <c r="D273" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E273" s="1">
         <v>1.34207508683015E-6</v>
@@ -9088,7 +9089,7 @@
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B274">
         <v>90772</v>
@@ -9097,7 +9098,7 @@
         <v>116237</v>
       </c>
       <c r="D274" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E274" s="1">
         <v>1.59766122253632E-6</v>
@@ -9117,7 +9118,7 @@
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B275">
         <v>90772</v>
@@ -9126,7 +9127,7 @@
         <v>116237</v>
       </c>
       <c r="D275" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E275" s="1">
         <v>4.7862431598509102E-6</v>
@@ -9146,7 +9147,7 @@
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B276">
         <v>90772</v>
@@ -9155,7 +9156,7 @@
         <v>116237</v>
       </c>
       <c r="D276" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E276" s="1">
         <v>6.7318941564749401E-6</v>
@@ -9175,7 +9176,7 @@
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B277">
         <v>90772</v>
@@ -9184,7 +9185,7 @@
         <v>116237</v>
       </c>
       <c r="D277" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E277" s="1">
         <v>9.1271556577834403E-6</v>
@@ -9204,7 +9205,7 @@
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B278">
         <v>90772</v>
@@ -9213,7 +9214,7 @@
         <v>116237</v>
       </c>
       <c r="D278" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E278" s="1">
         <v>1.0513712199126601E-5</v>
@@ -9233,7 +9234,7 @@
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B279">
         <v>90772</v>
@@ -9242,7 +9243,7 @@
         <v>116237</v>
       </c>
       <c r="D279" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E279" s="1">
         <v>3.8169740215185201E-5</v>
@@ -9262,7 +9263,7 @@
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B280">
         <v>90772</v>
@@ -9271,7 +9272,7 @@
         <v>116237</v>
       </c>
       <c r="D280" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E280">
         <v>2.5547259864598101E-4</v>
@@ -9291,7 +9292,7 @@
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B281">
         <v>90772</v>
@@ -9300,7 +9301,7 @@
         <v>116237</v>
       </c>
       <c r="D281" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E281">
         <v>2.5727402190952703E-4</v>
@@ -9320,7 +9321,7 @@
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B282">
         <v>90772</v>
@@ -9329,7 +9330,7 @@
         <v>116237</v>
       </c>
       <c r="D282" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E282">
         <v>5.7596509057818699E-4</v>
@@ -9349,7 +9350,7 @@
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B283">
         <v>90772</v>
@@ -9358,7 +9359,7 @@
         <v>116237</v>
       </c>
       <c r="D283" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E283">
         <v>2.88952575309535E-3</v>
@@ -9378,7 +9379,7 @@
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B284">
         <v>90772</v>
@@ -9387,7 +9388,7 @@
         <v>116237</v>
       </c>
       <c r="D284" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E284">
         <v>5.6388828871391404E-3</v>
@@ -9407,7 +9408,7 @@
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B285">
         <v>90772</v>
@@ -9416,7 +9417,7 @@
         <v>116237</v>
       </c>
       <c r="D285" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E285">
         <v>1.1030715465542599E-2</v>
@@ -9436,7 +9437,7 @@
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B286">
         <v>90772</v>
@@ -9445,7 +9446,7 @@
         <v>116237</v>
       </c>
       <c r="D286" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E286">
         <v>1.32768272891801E-2</v>
@@ -9465,7 +9466,7 @@
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B287">
         <v>90772</v>
@@ -9474,7 +9475,7 @@
         <v>116237</v>
       </c>
       <c r="D287" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E287">
         <v>3.6755989451759702E-2</v>
@@ -9494,7 +9495,7 @@
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B288">
         <v>90772</v>
@@ -9503,7 +9504,7 @@
         <v>116237</v>
       </c>
       <c r="D288" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E288">
         <v>3.9536754112522998E-2</v>
@@ -9523,7 +9524,7 @@
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B289">
         <v>90772</v>
@@ -9532,7 +9533,7 @@
         <v>116237</v>
       </c>
       <c r="D289" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E289">
         <v>8.2948016311189907E-2</v>
@@ -9552,7 +9553,7 @@
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B290">
         <v>90772</v>
@@ -9561,7 +9562,7 @@
         <v>116237</v>
       </c>
       <c r="D290" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E290">
         <v>0.97101505096983898</v>
